--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487642_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487642_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.344200000000001</v>
+        <v>8.8705</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4863</v>
+        <v>5.6855</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8579</v>
+        <v>3.185</v>
       </c>
       <c r="G2" t="n">
         <v>6.0922</v>
@@ -610,13 +610,13 @@
         <v>1.3582</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6503</v>
+        <v>1.1765</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3604</v>
+        <v>0.5596</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2898</v>
+        <v>0.6169</v>
       </c>
       <c r="V2" t="n">
         <v>2.1839</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. REAL BERMUDEZ</t>
+          <t>G. MARTIN LOPEZ-LAGO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6085</v>
+        <v>5.3826</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8821</v>
+        <v>2.18</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7264</v>
+        <v>3.2026</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5568</v>
+        <v>4.611</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4391</v>
+        <v>2.0712</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9959</v>
+        <v>2.5398</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0802</v>
+        <v>3.4791</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2595</v>
+        <v>2.9412</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3397</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4766</v>
+        <v>1.132</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1796</v>
+        <v>-0.87</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6562</v>
+        <v>2.002</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9702</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1642</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7517</v>
+        <v>0.1119</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8018999999999999</v>
+        <v>-0.1349</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9498</v>
+        <v>0.2468</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3299</v>
+        <v>0.6597</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3299</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. MARTIN LOPEZ-LAGO</t>
+          <t>A. REAL BERMUDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5184</v>
+        <v>4.3087</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4793</v>
+        <v>1.8821</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0391</v>
+        <v>2.4266</v>
       </c>
       <c r="G4" t="n">
-        <v>4.611</v>
+        <v>1.5568</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0712</v>
+        <v>-0.4391</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5398</v>
+        <v>1.9959</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4791</v>
+        <v>1.0802</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9412</v>
+        <v>-0.2595</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5377999999999999</v>
+        <v>1.3397</v>
       </c>
       <c r="M4" t="n">
-        <v>1.132</v>
+        <v>0.4766</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.87</v>
+        <v>-0.1796</v>
       </c>
       <c r="O4" t="n">
-        <v>2.002</v>
+        <v>0.6562</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.9702</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1642</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7523</v>
+        <v>1.4519</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8356</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0833</v>
+        <v>0.65</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6597</v>
+        <v>0.3299</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6597</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8247</v>
+        <v>3.1434</v>
       </c>
       <c r="E5" t="n">
         <v>1.786</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0387</v>
+        <v>1.3573</v>
       </c>
       <c r="G5" t="n">
         <v>3.1823</v>
@@ -844,13 +844,13 @@
         <v>0.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6902</v>
+        <v>1.0089</v>
       </c>
       <c r="T5" t="n">
         <v>-0.0471</v>
       </c>
       <c r="U5" t="n">
-        <v>1.7374</v>
+        <v>1.056</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6597</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.9657</v>
+        <v>2.5024</v>
       </c>
       <c r="E6" t="n">
         <v>0.1998</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7659</v>
+        <v>2.3026</v>
       </c>
       <c r="G6" t="n">
         <v>1.9661</v>
@@ -922,13 +922,13 @@
         <v>0.5821</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9814</v>
+        <v>1.5181</v>
       </c>
       <c r="T6" t="n">
         <v>0.1346</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8468</v>
+        <v>1.3835</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5937</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. HADI ADEGBITE</t>
+          <t>S. PARADELA PARIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8216</v>
+        <v>1.2494</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1439</v>
+        <v>0.1758</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9655</v>
+        <v>1.0737</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7965</v>
+        <v>0.0978</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6476</v>
+        <v>0.8519</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1489</v>
+        <v>-0.7541</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4849</v>
+        <v>0.187</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4037</v>
+        <v>0.1236</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0634</v>
       </c>
       <c r="M7" t="n">
-        <v>1.3116</v>
+        <v>-0.0892</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2439</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0677</v>
+        <v>-0.8175</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7761</v>
+        <v>0.5821</v>
       </c>
       <c r="S7" t="n">
-        <v>1.849</v>
+        <v>0.5036</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9713000000000001</v>
+        <v>-0.0112</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8778</v>
+        <v>0.5148</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6597</v>
+        <v>0.066</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6597</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ROLDAN DE LA PORTILLA</t>
+          <t>O. HADI ADEGBITE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7979000000000001</v>
+        <v>1.2304</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2063</v>
+        <v>-1.5443</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4084</v>
+        <v>2.7747</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9335</v>
+        <v>1.7965</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0404</v>
+        <v>0.6476</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8931</v>
+        <v>1.1489</v>
       </c>
       <c r="J8" t="n">
-        <v>1.641</v>
+        <v>0.4849</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0092</v>
+        <v>0.4037</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6318</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7075</v>
+        <v>1.3116</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9689</v>
+        <v>0.2439</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2614</v>
+        <v>1.0677</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5821</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.194</v>
+        <v>-1.9403</v>
       </c>
       <c r="R8" t="n">
         <v>0.7761</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1581</v>
+        <v>1.2578</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1951</v>
+        <v>0.5709</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.037</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8758</v>
+        <v>-0.6597</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5642</v>
+        <v>-0.6597</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. PARADELA PARIS</t>
+          <t>A. ROLDAN DE LA PORTILLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5765</v>
+        <v>0.5977</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2246</v>
+        <v>2.0061</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8011</v>
+        <v>-1.4084</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0978</v>
+        <v>0.9335</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8519</v>
+        <v>0.0404</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7541</v>
+        <v>0.8931</v>
       </c>
       <c r="J9" t="n">
-        <v>0.187</v>
+        <v>1.641</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1236</v>
+        <v>1.0092</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0634</v>
+        <v>0.6318</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0892</v>
+        <v>-0.7075</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7282999999999999</v>
+        <v>-0.9689</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8175</v>
+        <v>0.2614</v>
       </c>
       <c r="P9" t="n">
         <v>0.5821</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1694</v>
+        <v>-0.0421</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4116</v>
+        <v>-0.0051</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2423</v>
+        <v>-0.037</v>
       </c>
       <c r="V9" t="n">
-        <v>0.066</v>
+        <v>-0.8758</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X9" t="n">
-        <v>0.066</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
+          <t>P. ESTEBANEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6056</v>
+        <v>-0.1757</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0319</v>
+        <v>0.8162</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5736</v>
+        <v>-0.9918</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5154</v>
+        <v>-0.7663</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6311</v>
+        <v>-2.1816</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1157</v>
+        <v>1.4153</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2092</v>
+        <v>0.4487</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0824</v>
+        <v>-0.3048</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1268</v>
+        <v>0.7536</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7246</v>
+        <v>-1.215</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7135</v>
+        <v>-1.8768</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0111</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5821</v>
+        <v>0.5821</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3881</v>
+        <v>0.7761</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4919</v>
+        <v>-0.3213</v>
       </c>
       <c r="T10" t="n">
-        <v>0.729</v>
+        <v>-0.3326</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2371</v>
+        <v>0.0112</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3299</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. ESTEBANEZ GONZALEZ</t>
+          <t>D. MARINEZ FERNANDEZ-URRUTIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7029</v>
+        <v>-0.8519</v>
       </c>
       <c r="E11" t="n">
-        <v>0.616</v>
+        <v>-0.6325</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3189</v>
+        <v>-0.2193</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7663</v>
+        <v>-0.5154</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1816</v>
+        <v>-0.6311</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4153</v>
+        <v>0.1157</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4487</v>
+        <v>0.2092</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3048</v>
+        <v>0.0824</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7536</v>
+        <v>0.1268</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.215</v>
+        <v>-0.7246</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8768</v>
+        <v>-0.7135</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6618000000000001</v>
+        <v>-0.0111</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5821</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7761</v>
+        <v>0.3881</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8486</v>
+        <v>0.2456</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5328000000000001</v>
+        <v>0.1284</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3158</v>
+        <v>0.1172</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3299</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.5841</v>
+        <v>-1.2476</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7697</v>
+        <v>-1.5695</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1856</v>
+        <v>0.3219</v>
       </c>
       <c r="G12" t="n">
         <v>0.6325</v>
@@ -1390,13 +1390,13 @@
         <v>0.5821</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0303</v>
+        <v>0.3062</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4845</v>
+        <v>-0.2843</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4542</v>
+        <v>0.5905</v>
       </c>
       <c r="V12" t="n">
         <v>-0.828</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.3335</v>
+        <v>-4.7784</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.0931</v>
+        <v>-3.5926</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2403</v>
+        <v>-1.1858</v>
       </c>
       <c r="G13" t="n">
         <v>-4.0414</v>
@@ -1468,13 +1468,13 @@
         <v>0.9702</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7398</v>
+        <v>-0.1848</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7145</v>
+        <v>-0.214</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0253</v>
+        <v>0.0292</v>
       </c>
       <c r="V13" t="n">
         <v>0.6119</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>20.2314</v>
+        <v>20.2315</v>
       </c>
       <c r="E14" t="n">
-        <v>7.392599999999998</v>
+        <v>7.392600000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>12.839</v>
+        <v>12.8391</v>
       </c>
       <c r="G14" t="n">
         <v>15.5456</v>
@@ -1528,7 +1528,7 @@
         <v>9.593300000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7041999999999993</v>
+        <v>0.7042000000000006</v>
       </c>
       <c r="N14" t="n">
         <v>-5.1905</v>
@@ -1546,13 +1546,13 @@
         <v>9.701600000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>7.0322</v>
+        <v>7.0323</v>
       </c>
       <c r="T14" t="n">
         <v>1.1662</v>
       </c>
       <c r="U14" t="n">
-        <v>5.8662</v>
+        <v>5.8661</v>
       </c>
       <c r="V14" t="n">
         <v>0.5643999999999998</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2943</v>
+        <v>0.4216</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.7917</v>
+        <v>-1.6916</v>
       </c>
       <c r="F15" t="n">
-        <v>2.086</v>
+        <v>2.1133</v>
       </c>
       <c r="G15" t="n">
         <v>-1.794</v>
@@ -1624,13 +1624,13 @@
         <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7939000000000001</v>
+        <v>-0.6665</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7145</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0794</v>
+        <v>-0.0521</v>
       </c>
       <c r="V15" t="n">
         <v>0.9418</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. OILLATAGUERRE</t>
+          <t>E. ECHEVERRIA MATEO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1652</v>
+        <v>-0.2026</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4165</v>
+        <v>-2.0112</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2513</v>
+        <v>1.8086</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2174</v>
+        <v>-1.4967</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0527</v>
+        <v>0.3073</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2702</v>
+        <v>-1.804</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6812</v>
+        <v>-1.1669</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7168</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0356</v>
+        <v>-1.2535</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.8987</v>
+        <v>-0.3298</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6641</v>
+        <v>0.2208</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.2346</v>
+        <v>-0.5506</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9702</v>
+        <v>1.7463</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9702</v>
+        <v>1.7463</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4125</v>
+        <v>-0.4999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5114</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0989</v>
+        <v>0.3443</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.0478</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2239</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1235</v>
+        <v>-0.2081</v>
       </c>
       <c r="E17" t="n">
         <v>-0.1805</v>
       </c>
       <c r="F17" t="n">
-        <v>0.057</v>
+        <v>-0.0275</v>
       </c>
       <c r="G17" t="n">
         <v>1.1492</v>
@@ -1780,13 +1780,13 @@
         <v>1.7463</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1451</v>
+        <v>0.0606</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1559</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3011</v>
+        <v>0.2165</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2239</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. ECHEVERRIA MATEO</t>
+          <t>M. OILLATAGUERRE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3328</v>
+        <v>-0.2319</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7109</v>
+        <v>1.916</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3782</v>
+        <v>-2.1479</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4967</v>
+        <v>-1.2174</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3073</v>
+        <v>0.0527</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.804</v>
+        <v>-1.2702</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1669</v>
+        <v>0.6812</v>
       </c>
       <c r="K18" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.7168</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2535</v>
+        <v>-0.0356</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3298</v>
+        <v>-1.8987</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2208</v>
+        <v>-0.6641</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5506</v>
+        <v>-1.2346</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7463</v>
+        <v>0.9702</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7463</v>
+        <v>0.9702</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6301</v>
+        <v>0.0154</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.544</v>
+        <v>0.0109</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0861</v>
+        <v>0.0045</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0478</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0478</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7988</v>
+        <v>-0.3077</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4501</v>
+        <v>-0.1498</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3487</v>
+        <v>-0.1579</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5299</v>
@@ -1936,13 +1936,13 @@
         <v>1.3582</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8912</v>
+        <v>-0.4001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5204</v>
+        <v>-0.2201</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3708</v>
+        <v>-0.18</v>
       </c>
       <c r="V19" t="n">
         <v>0.2343</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1155</v>
+        <v>-1.6272</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4444</v>
+        <v>-1.1441</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6711</v>
+        <v>-0.4831</v>
       </c>
       <c r="G20" t="n">
         <v>-1.006</v>
@@ -2014,13 +2014,13 @@
         <v>0.7761</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3035</v>
+        <v>0.1848</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2423</v>
+        <v>0.058</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0612</v>
+        <v>0.1267</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6119</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1636</v>
+        <v>-1.6754</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4975</v>
+        <v>-0.1972</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6662</v>
+        <v>-1.4782</v>
       </c>
       <c r="G21" t="n">
         <v>-3.6724</v>
@@ -2092,13 +2092,13 @@
         <v>1.3582</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6853</v>
+        <v>-1.197</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.393</v>
+        <v>-1.0927</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2923</v>
+        <v>-0.1043</v>
       </c>
       <c r="V21" t="n">
         <v>1.8358</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ MORAN</t>
+          <t>M. MANGUE NVOMO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4805</v>
+        <v>-2.2255</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3719</v>
+        <v>-2.1774</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1086</v>
+        <v>-0.0481</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1325</v>
+        <v>-1.6877</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.9929</v>
+        <v>-0.968</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1396</v>
+        <v>-0.7196</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7008</v>
+        <v>-0.6411</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2564</v>
+        <v>-0.6055</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5556</v>
+        <v>-0.0356</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4317</v>
+        <v>-1.0466</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7366</v>
+        <v>-0.3625</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6952</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7761</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7463</v>
+        <v>0.3881</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8421</v>
+        <v>-0.6155</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.701</v>
+        <v>-0.5661</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1411</v>
+        <v>-0.0493</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2821</v>
+        <v>0.6597</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2821</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. MANGUE NVOMO</t>
+          <t>V. FERNANDEZ MORAN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5681</v>
+        <v>-2.52</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2775</v>
+        <v>-2.5721</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2906</v>
+        <v>0.0521</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6877</v>
+        <v>-2.1325</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.968</v>
+        <v>-1.9929</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7196</v>
+        <v>-0.1396</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6411</v>
+        <v>-0.7008</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6055</v>
+        <v>-1.2564</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0356</v>
+        <v>0.5556</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0466</v>
+        <v>-1.4317</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3625</v>
+        <v>-0.7366</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.6952</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5821</v>
+        <v>0.7761</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3881</v>
+        <v>1.7463</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.958</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6662</v>
+        <v>-0.9012</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2918</v>
+        <v>0.0197</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6597</v>
+        <v>-0.2821</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.6597</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.5733</v>
+        <v>-2.546</v>
       </c>
       <c r="E24" t="n">
         <v>-1.0103</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.563</v>
+        <v>-1.5358</v>
       </c>
       <c r="G24" t="n">
         <v>-1.4727</v>
@@ -2326,13 +2326,13 @@
         <v>0.194</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0126</v>
+        <v>-0.9853</v>
       </c>
       <c r="T24" t="n">
         <v>-0.6662</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3463</v>
+        <v>-0.3191</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2821</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.7002</v>
+        <v>-3.7547</v>
       </c>
       <c r="E25" t="n">
         <v>-2.2831</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4171</v>
+        <v>-1.4716</v>
       </c>
       <c r="G25" t="n">
         <v>-2.1721</v>
@@ -2404,13 +2404,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5579</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="T25" t="n">
         <v>-0.7268</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1689</v>
+        <v>0.1144</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.8347</v>
+        <v>-4.0194</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.2375</v>
+        <v>-1.3376</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.5972</v>
+        <v>-2.6818</v>
       </c>
       <c r="G26" t="n">
         <v>0.4867</v>
@@ -2482,13 +2482,13 @@
         <v>0.3881</v>
       </c>
       <c r="S26" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.1001</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0471</v>
+        <v>-0.1472</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1317</v>
+        <v>0.0471</v>
       </c>
       <c r="V26" t="n">
         <v>-1.8836</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-20.2315</v>
+        <v>-18.8969</v>
       </c>
       <c r="E27" t="n">
         <v>-12.8389</v>
       </c>
       <c r="F27" t="n">
-        <v>-7.392600000000001</v>
+        <v>-6.0579</v>
       </c>
       <c r="G27" t="n">
         <v>-15.5455</v>
@@ -2536,7 +2536,7 @@
         <v>-0.7040999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>5.1905</v>
+        <v>5.190499999999998</v>
       </c>
       <c r="L27" t="n">
         <v>-5.8947</v>
@@ -2551,7 +2551,7 @@
         <v>-9.593299999999999</v>
       </c>
       <c r="P27" t="n">
-        <v>2.9105</v>
+        <v>2.910499999999999</v>
       </c>
       <c r="Q27" t="n">
         <v>-9.701799999999999</v>
@@ -2560,16 +2560,16 @@
         <v>12.6121</v>
       </c>
       <c r="S27" t="n">
-        <v>-7.0324</v>
+        <v>-5.6976</v>
       </c>
       <c r="T27" t="n">
-        <v>-5.866000000000001</v>
+        <v>-5.866</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.1662</v>
+        <v>0.1684</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.5641999999999998</v>
+        <v>-0.5642000000000005</v>
       </c>
       <c r="W27" t="n">
         <v>3.4328</v>
